--- a/tools/excel/3xlsx/task.xlsx
+++ b/tools/excel/3xlsx/task.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,16 @@
           <t>排序权重</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>奖励体力</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>任务类型</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -499,6 +509,16 @@
           <t>sortPriority</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>rewardEnergy</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>objType</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -541,6 +561,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>uint</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -583,34 +613,56 @@
           <t>all</t>
         </is>
       </c>
-    </row>
-    <row r="5"/>
-    <row r="6"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="n">
         <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>使用线索道具</t>
+          <t>每日登录</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>4001</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
       </c>
       <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -620,194 +672,168 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>使用雷达道具</t>
+          <t>观看5次广告</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>4002</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>使用情报道具</t>
+          <t>连续登录3天</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>3001</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="n">
-        <v>100</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3</v>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>三星过关</t>
+          <t>击杀30只动物</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1002</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>100</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>击中飞碟</t>
+          <t>观看20次广告</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>累计击杀动物</t>
+          <t>获得武器</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>2001</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>102</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>通关常规关卡</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="n">
-        <v>2002</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>500</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>103</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>收集远古信物</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>4001</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3</v>
+      <c r="J12" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel/3xlsx/task.xlsx
+++ b/tools/excel/3xlsx/task.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,11 @@
           <t>任务类型</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>图标路径</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -519,6 +524,11 @@
           <t>objType</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>iconPath</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -571,6 +581,11 @@
           <t>uint</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -621,6 +636,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>all</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>client</t>
         </is>
       </c>
     </row>
